--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0018.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0018.xlsx
@@ -12706,7 +12706,7 @@
 Xa Xôi: Mắt.
 Gió: Tai.
 Dài: Chân.
-Xanh: Weapons.
+Xanh: Vũ khí.
 Thanh: Súng.
 ...</t>
         </is>
@@ -27479,7 +27479,7 @@
       <c r="M405" t="inlineStr">
         <is>
           <t>Theo truyền thuyết, Thorncrown Rises tại Thessaleo Fells lưu giữ vinh quang đã mất của gia tộc Fisalia. 
-Qua từng Dodget cọ tinh tế của người họa sĩ, ta có thể cảm nhận được nỗi buồn bã và hoang mang trong lòng nàng.</t>
+Qua từng nét cọ tinh tế của người họa sĩ, ta có thể cảm nhận được nỗi buồn bã và hoang mang trong lòng nàng.</t>
         </is>
       </c>
     </row>
@@ -28145,7 +28145,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Khi năm cũ sắp qua, những người bạn từ khắp nơi đã tụ họp về đây theo lời mời của ngươi để cùng nhau trải qua những khoảnh khắc quý giá. Điều ước ngươi từng khát khao sẽ được thực hiện khi mùa xuân đến. Mong rằng hành trình của ngươi sẽ tràn đầy hy vọng và niềm vui, và tất cả Rover trên mảnh đất này sẽ luôn tìm thấy một mái nhà để trở về.</t>
+          <t>Khi năm cũ sắp qua, những người bạn từ khắp nơi đã tụ họp về đây theo lời mời của ngươi để cùng nhau trải qua những khoảnh khắc quý giá. Điều ước ngươi từng khát khao sẽ được thực hiện khi mùa xuân đến. Mong rằng hành trình của ngươi sẽ tràn đầy hy vọng và niềm vui, và tất cả Vận Mệnh Giả trên mảnh đất này sẽ luôn tìm thấy một mái nhà để trở về.</t>
         </is>
       </c>
     </row>
@@ -28210,7 +28210,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Khi năm cũ sắp qua, những người bạn từ khắp nơi đã tụ họp về đây theo lời mời của ngươi để cùng nhau trải qua những khoảnh khắc quý giá. Điều ước ngươi từng khát khao sẽ được thực hiện khi mùa xuân đến. Mong rằng hành trình của ngươi sẽ tràn đầy hy vọng và niềm vui, và tất cả Rover trên mảnh đất này sẽ luôn tìm thấy một mái nhà để trở về.</t>
+          <t>Khi năm cũ sắp qua, những người bạn từ khắp nơi đã tụ họp về đây theo lời mời của ngươi để cùng nhau trải qua những khoảnh khắc quý giá. Điều ước ngươi từng khát khao sẽ được thực hiện khi mùa xuân đến. Mong rằng hành trình của ngươi sẽ tràn đầy hy vọng và niềm vui, và tất cả Vận Mệnh Giả trên mảnh đất này sẽ luôn tìm thấy một mái nhà để trở về.</t>
         </is>
       </c>
     </row>
@@ -30631,7 +30631,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Quyển sketchbook kỳ quái, từng trang ghi lại một khúc ca ám ảnh, Dodget chữ xoắn vặn như bị ma ám. Những tưởng tượng sống động ngày nào giờ chỉ còn là giọt nước mắt lặng thầm, nhỏ xuống bề mặt, để lại những vết ố mờ nhạt nhưng đau lòng.</t>
+          <t>Quyển sketchbook kỳ quái, từng trang ghi lại một khúc ca ám ảnh, nét chữ xoắn vặn như bị ma ám. Những tưởng tượng sống động ngày nào giờ chỉ còn là giọt nước mắt lặng thầm, nhỏ xuống bề mặt, để lại những vết ố mờ nhạt nhưng đau lòng.</t>
         </is>
       </c>
     </row>
@@ -33750,7 +33750,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Một lá thư viết tay từ chính Augusta. Dodget chữ uyển chuyển nhưng lại có chút ngập ngừng, như thể từng từ được cân nhắc kỹ lưỡng trước khi đặt bút.</t>
+          <t>Một lá thư viết tay từ chính Augusta. Nét chữ uyển chuyển nhưng lại có chút ngập ngừng, như thể từng từ được cân nhắc kỹ lưỡng trước khi đặt bút.</t>
         </is>
       </c>
     </row>
